--- a/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
+++ b/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
@@ -504,22 +504,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5460.5293934</v>
+        <v>3124.65276</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -528,17 +528,17 @@
         <v>3184.447149</v>
       </c>
       <c r="L2" t="n">
-        <v>23.9177556</v>
+        <v>59.794389</v>
       </c>
       <c r="M2" t="n">
-        <v>15116</v>
+        <v>21000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -553,22 +553,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5223.273808400001</v>
+        <v>2890.006356</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2300.000000000001</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -577,17 +577,17 @@
         <v>2945.45211</v>
       </c>
       <c r="L3" t="n">
-        <v>22.1783016</v>
+        <v>55.445754</v>
       </c>
       <c r="M3" t="n">
-        <v>17232</v>
+        <v>21000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -602,22 +602,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5470.844100600001</v>
+        <v>3147.920818</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2300.000000000001</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -626,17 +626,17 @@
         <v>3186.126289</v>
       </c>
       <c r="L4" t="n">
-        <v>15.2821884</v>
+        <v>38.205471</v>
       </c>
       <c r="M4" t="n">
-        <v>19348</v>
+        <v>21000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3537.1701852</v>
+        <v>3534.469818</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -675,10 +675,10 @@
         <v>3538.97043</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8002448</v>
+        <v>4.500612</v>
       </c>
       <c r="M5" t="n">
-        <v>19348</v>
+        <v>21000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3284.7155694</v>
+        <v>3284.069634</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -724,10 +724,10 @@
         <v>3285.146193</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4306236</v>
+        <v>1.076559</v>
       </c>
       <c r="M6" t="n">
-        <v>19348</v>
+        <v>21000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3615.5594156</v>
+        <v>3561.004652</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>3651.929258</v>
       </c>
       <c r="L7" t="n">
-        <v>36.3698424</v>
+        <v>90.92460600000001</v>
       </c>
       <c r="M7" t="n">
-        <v>19348</v>
+        <v>21000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -798,22 +798,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3135.4680054</v>
+        <v>9299.333150970719</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>6491.39307897072</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -822,17 +822,17 @@
         <v>3353.819961</v>
       </c>
       <c r="L8" t="n">
-        <v>218.3519556</v>
+        <v>545.8798889999999</v>
       </c>
       <c r="M8" t="n">
-        <v>19348</v>
+        <v>26852.64</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -847,22 +847,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3620.4375184</v>
+        <v>9600.354067</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -871,17 +871,17 @@
         <v>4233.826486</v>
       </c>
       <c r="L9" t="n">
-        <v>613.3889676</v>
+        <v>1533.472419</v>
       </c>
       <c r="M9" t="n">
-        <v>19348</v>
+        <v>33073.68</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -896,22 +896,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5638.3908032</v>
+        <v>10618.720658</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -920,17 +920,17 @@
         <v>6918.1709</v>
       </c>
       <c r="L10" t="n">
-        <v>1279.7800968</v>
+        <v>3199.450242</v>
       </c>
       <c r="M10" t="n">
-        <v>19348</v>
+        <v>39360.96</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>9218.2464812</v>
+        <v>12610.241243</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -969,17 +969,17 @@
         <v>11556.91664</v>
       </c>
       <c r="L11" t="n">
-        <v>2338.6701588</v>
+        <v>5846.675397</v>
       </c>
       <c r="M11" t="n">
-        <v>19347.99999999999</v>
+        <v>45648.24</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -994,22 +994,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>8540.745832000001</v>
+        <v>9905.957892999999</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1018,17 +1018,17 @@
         <v>12230.60446</v>
       </c>
       <c r="L12" t="n">
-        <v>3689.858628</v>
+        <v>9224.646567</v>
       </c>
       <c r="M12" t="n">
-        <v>19347.99999999999</v>
+        <v>51935.52</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1043,22 +1043,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>7064.695748</v>
+        <v>6741.778453000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>79.11077299999988</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1067,17 +1067,17 @@
         <v>11932.71446</v>
       </c>
       <c r="L13" t="n">
-        <v>4868.018712</v>
+        <v>12170.04678</v>
       </c>
       <c r="M13" t="n">
-        <v>19347.99999999998</v>
+        <v>58222.8</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1092,22 +1092,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5388.178596</v>
+        <v>1264.98256</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2070.03488</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1116,17 +1116,17 @@
         <v>11050.33254</v>
       </c>
       <c r="L14" t="n">
-        <v>5662.153944</v>
+        <v>14155.38486</v>
       </c>
       <c r="M14" t="n">
-        <v>19347.99999999998</v>
+        <v>60296.48</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1141,22 +1141,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3425.492891</v>
+        <v>440.4142839999986</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3719.171433</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2299.999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1165,17 +1165,17 @@
         <v>9428.32625</v>
       </c>
       <c r="L15" t="n">
-        <v>6002.833359</v>
+        <v>15007.083399</v>
       </c>
       <c r="M15" t="n">
-        <v>19347.99999999997</v>
+        <v>62370.16</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1190,22 +1190,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4629.301893</v>
+        <v>5258.290890000006</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2252.269341</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6900.000000000005</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1214,17 +1214,17 @@
         <v>10311.48879</v>
       </c>
       <c r="L16" t="n">
-        <v>5682.186897</v>
+        <v>14205.467241</v>
       </c>
       <c r="M16" t="n">
-        <v>19347.99999999996</v>
+        <v>68591.2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1239,22 +1239,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>6159.669926</v>
+        <v>6035.633061</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>604.2166510000006</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1263,17 +1263,17 @@
         <v>11245.17227</v>
       </c>
       <c r="L17" t="n">
-        <v>5085.502344</v>
+        <v>12713.75586</v>
       </c>
       <c r="M17" t="n">
-        <v>19347.99999999996</v>
+        <v>74878.48</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1288,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4850.243495999999</v>
+        <v>6252.399288</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>415.9257450000005</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1312,17 +1312,17 @@
         <v>8792.756796</v>
       </c>
       <c r="L18" t="n">
-        <v>3942.5133</v>
+        <v>9856.283253000001</v>
       </c>
       <c r="M18" t="n">
-        <v>19347.99999999996</v>
+        <v>81099.52</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>IDLE</t>
+          <t>ARB (Charge)</t>
         </is>
       </c>
     </row>
@@ -1337,22 +1337,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8185.227126400001</v>
+        <v>6775.314167999956</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>62.34291600000006</v>
       </c>
       <c r="I19" t="n">
-        <v>4600.000000000002</v>
+        <v>6899.999999999956</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1361,10 +1361,10 @@
         <v>6100.064376</v>
       </c>
       <c r="L19" t="n">
-        <v>2514.8372496</v>
+        <v>6287.093124000001</v>
       </c>
       <c r="M19" t="n">
-        <v>23579.99999999995</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1386,22 +1386,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>7909.437807</v>
+        <v>1707.642818</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1410,17 +1410,17 @@
         <v>4377.301133</v>
       </c>
       <c r="L20" t="n">
-        <v>1067.863326</v>
+        <v>2669.658315</v>
       </c>
       <c r="M20" t="n">
-        <v>27811.99999999994</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>8009.422293400001</v>
+        <v>3081.917022</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4600.000000000001</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1459,17 +1459,17 @@
         <v>3627.759141</v>
       </c>
       <c r="L21" t="n">
-        <v>218.3368476</v>
+        <v>545.842119</v>
       </c>
       <c r="M21" t="n">
-        <v>32043.99999999994</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>8318.310329200001</v>
+        <v>3683.151408000001</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4600.000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1508,17 +1508,17 @@
         <v>3741.74961</v>
       </c>
       <c r="L22" t="n">
-        <v>23.4392808</v>
+        <v>58.598202</v>
       </c>
       <c r="M22" t="n">
-        <v>36275.99999999993</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>8273.404266600002</v>
+        <v>3639.581741</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4600.000000000002</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1557,17 +1557,17 @@
         <v>3695.952617</v>
       </c>
       <c r="L23" t="n">
-        <v>22.5483504</v>
+        <v>56.370876</v>
       </c>
       <c r="M23" t="n">
-        <v>40507.99999999993</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -1582,22 +1582,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8418.950392600002</v>
+        <v>3781.168326</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4600.000000000002</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1606,17 +1606,17 @@
         <v>3844.138437</v>
       </c>
       <c r="L24" t="n">
-        <v>25.1880444</v>
+        <v>62.970111</v>
       </c>
       <c r="M24" t="n">
-        <v>44739.99999999992</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>
@@ -1631,22 +1631,22 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8205.900164000001</v>
+        <v>3566.863906</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1655,17 +1655,17 @@
         <v>3631.924336</v>
       </c>
       <c r="L25" t="n">
-        <v>26.024172</v>
+        <v>65.06043</v>
       </c>
       <c r="M25" t="n">
-        <v>48971.99999999991</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N25" t="n">
-        <v>51841</v>
+        <v>11679.44000000004</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>ARB (Charge)</t>
+          <t>IDLE</t>
         </is>
       </c>
     </row>

--- a/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
+++ b/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,84 +429,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Instante</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Preco_Importacao</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Preco_Exportacao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>VEs_Ligados_Total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>VEs_a_Carregar</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>VEs_a_Descarregar</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rede_Importacao_kW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Rede_Exportacao_kW</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>VE_Carga_kW</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>VE_Descarga_kW</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Instalacao_PL_kW</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Solar_PV_kW</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Energia_Armazenada_VEs_kWh</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Falhas_Relaxamento_kWh</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Modo_Operacao</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -543,7 +555,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
@@ -641,7 +653,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
@@ -690,7 +702,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
@@ -739,7 +751,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
@@ -788,7 +800,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
@@ -813,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>6491.39307897072</v>
+        <v>6491.393078970719</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -837,7 +849,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
@@ -886,7 +898,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
@@ -935,7 +947,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
@@ -984,7 +996,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="n">
@@ -1021,7 +1033,7 @@
         <v>9224.646567</v>
       </c>
       <c r="M12" t="n">
-        <v>51935.52</v>
+        <v>51869.28</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="n">
@@ -1070,7 +1082,7 @@
         <v>12170.04678</v>
       </c>
       <c r="M13" t="n">
-        <v>58222.8</v>
+        <v>58090.32</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1082,7 +1094,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="n">
@@ -1119,7 +1131,7 @@
         <v>14155.38486</v>
       </c>
       <c r="M14" t="n">
-        <v>60296.48</v>
+        <v>60164</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1131,7 +1143,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="n">
@@ -1150,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>440.4142839999986</v>
+        <v>440.4142839999995</v>
       </c>
       <c r="H15" t="n">
         <v>3719.171433</v>
       </c>
       <c r="I15" t="n">
-        <v>2299.999999999999</v>
+        <v>2300</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1168,7 +1180,7 @@
         <v>15007.083399</v>
       </c>
       <c r="M15" t="n">
-        <v>62370.16</v>
+        <v>62237.68</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1180,7 +1192,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="n">
@@ -1199,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5258.290890000006</v>
+        <v>5258.29089</v>
       </c>
       <c r="H16" t="n">
         <v>2252.269341</v>
       </c>
       <c r="I16" t="n">
-        <v>6900.000000000005</v>
+        <v>6900</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1217,7 +1229,7 @@
         <v>14205.467241</v>
       </c>
       <c r="M16" t="n">
-        <v>68591.2</v>
+        <v>68524.95999999999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1229,7 +1241,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="n">
@@ -1266,7 +1278,7 @@
         <v>12713.75586</v>
       </c>
       <c r="M17" t="n">
-        <v>74878.48</v>
+        <v>74746</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1278,7 +1290,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
@@ -1315,7 +1327,7 @@
         <v>9856.283253000001</v>
       </c>
       <c r="M18" t="n">
-        <v>81099.52</v>
+        <v>81033.28</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1327,7 +1339,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="n">
@@ -1346,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>6775.314167999956</v>
+        <v>6775.314168</v>
       </c>
       <c r="H19" t="n">
         <v>62.34291600000006</v>
       </c>
       <c r="I19" t="n">
-        <v>6899.999999999956</v>
+        <v>6900</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1364,7 +1376,7 @@
         <v>6287.093124000001</v>
       </c>
       <c r="M19" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1376,7 +1388,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="n">
@@ -1413,7 +1425,7 @@
         <v>2669.658315</v>
       </c>
       <c r="M20" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="n">
@@ -1462,7 +1474,7 @@
         <v>545.842119</v>
       </c>
       <c r="M21" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
@@ -1511,7 +1523,7 @@
         <v>58.598202</v>
       </c>
       <c r="M22" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1523,7 +1535,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="n">
@@ -1560,7 +1572,7 @@
         <v>56.370876</v>
       </c>
       <c r="M23" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1572,7 +1584,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="n">
@@ -1609,7 +1621,7 @@
         <v>62.970111</v>
       </c>
       <c r="M24" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1621,7 +1633,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="n">
@@ -1658,10 +1670,10 @@
         <v>65.06043</v>
       </c>
       <c r="M25" t="n">
-        <v>87320.55999999995</v>
+        <v>87320.56</v>
       </c>
       <c r="N25" t="n">
-        <v>11679.44000000004</v>
+        <v>11679.44</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>

--- a/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
+++ b/RESULTS_3/Gestao_Energia_e_Veiculos_Final.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,84 +417,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Instante</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Preco_Importacao</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Preco_Exportacao</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>VEs_Ligados_Total</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>VEs_a_Carregar</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>VEs_a_Descarregar</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Rede_Importacao_kW</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Rede_Exportacao_kW</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>VE_Carga_kW</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>VE_Descarga_kW</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Instalacao_PL_kW</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Solar_PV_kW</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Energia_Armazenada_VEs_kWh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Falhas_Relaxamento_kWh</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Modo_Operacao</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -555,7 +543,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
@@ -604,7 +592,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
@@ -653,7 +641,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
@@ -702,7 +690,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
@@ -751,7 +739,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
@@ -800,7 +788,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
@@ -825,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>6491.393078970719</v>
+        <v>6491.39307897072</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -849,7 +837,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
@@ -898,7 +886,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
@@ -947,7 +935,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
@@ -996,7 +984,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="n">
@@ -1033,7 +1021,7 @@
         <v>9224.646567</v>
       </c>
       <c r="M12" t="n">
-        <v>51869.28</v>
+        <v>51935.52</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="n">
@@ -1082,7 +1070,7 @@
         <v>12170.04678</v>
       </c>
       <c r="M13" t="n">
-        <v>58090.32</v>
+        <v>58222.8</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1094,7 +1082,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="n">
@@ -1131,7 +1119,7 @@
         <v>14155.38486</v>
       </c>
       <c r="M14" t="n">
-        <v>60164</v>
+        <v>60296.48</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1143,7 +1131,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="n">
@@ -1162,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>440.4142839999995</v>
+        <v>440.4142839999986</v>
       </c>
       <c r="H15" t="n">
         <v>3719.171433</v>
       </c>
       <c r="I15" t="n">
-        <v>2300</v>
+        <v>2299.999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1180,7 +1168,7 @@
         <v>15007.083399</v>
       </c>
       <c r="M15" t="n">
-        <v>62237.68</v>
+        <v>62370.16</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1192,7 +1180,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="n">
@@ -1211,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5258.29089</v>
+        <v>5258.290890000006</v>
       </c>
       <c r="H16" t="n">
         <v>2252.269341</v>
       </c>
       <c r="I16" t="n">
-        <v>6900</v>
+        <v>6900.000000000005</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1229,7 +1217,7 @@
         <v>14205.467241</v>
       </c>
       <c r="M16" t="n">
-        <v>68524.95999999999</v>
+        <v>68591.2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1241,7 +1229,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="n">
@@ -1278,7 +1266,7 @@
         <v>12713.75586</v>
       </c>
       <c r="M17" t="n">
-        <v>74746</v>
+        <v>74878.48</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1290,7 +1278,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
@@ -1327,7 +1315,7 @@
         <v>9856.283253000001</v>
       </c>
       <c r="M18" t="n">
-        <v>81033.28</v>
+        <v>81099.52</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1339,7 +1327,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="n">
@@ -1358,13 +1346,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>6775.314168</v>
+        <v>6775.314167999956</v>
       </c>
       <c r="H19" t="n">
         <v>62.34291600000006</v>
       </c>
       <c r="I19" t="n">
-        <v>6900</v>
+        <v>6899.999999999956</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1376,7 +1364,7 @@
         <v>6287.093124000001</v>
       </c>
       <c r="M19" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1388,7 +1376,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="n">
@@ -1425,7 +1413,7 @@
         <v>2669.658315</v>
       </c>
       <c r="M20" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="n">
@@ -1474,7 +1462,7 @@
         <v>545.842119</v>
       </c>
       <c r="M21" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1486,7 +1474,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
@@ -1523,7 +1511,7 @@
         <v>58.598202</v>
       </c>
       <c r="M22" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1535,7 +1523,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="n">
@@ -1572,7 +1560,7 @@
         <v>56.370876</v>
       </c>
       <c r="M23" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1584,7 +1572,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="n">
@@ -1621,7 +1609,7 @@
         <v>62.970111</v>
       </c>
       <c r="M24" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1633,7 +1621,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="n">
@@ -1670,10 +1658,10 @@
         <v>65.06043</v>
       </c>
       <c r="M25" t="n">
-        <v>87320.56</v>
+        <v>87320.55999999995</v>
       </c>
       <c r="N25" t="n">
-        <v>11679.44</v>
+        <v>11679.44000000004</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
